--- a/e2e/downloadedFile/Non_Regular_Salary_BFKJ_Q1.xlsx
+++ b/e2e/downloadedFile/Non_Regular_Salary_BFKJ_Q1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
   <si>
     <t>DAFTAR PEMBAYARAN</t>
   </si>
@@ -62,115 +62,100 @@
     <t>MAR</t>
   </si>
   <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>550,00</t>
+  </si>
+  <si>
+    <t>1.650,00</t>
+  </si>
+  <si>
+    <t>115,00</t>
+  </si>
+  <si>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>0,00</t>
+  </si>
+  <si>
+    <t>1.100,00</t>
+  </si>
+  <si>
+    <t>60,00</t>
+  </si>
+  <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
+    <t>RIMBUN SIBURIAN</t>
+  </si>
+  <si>
+    <t>100,00</t>
+  </si>
+  <si>
+    <t>300,00</t>
+  </si>
+  <si>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
+    <t>Expat</t>
+  </si>
+  <si>
+    <t>SYALDY KHARISMA ANANDA</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>200,00</t>
+  </si>
+  <si>
+    <t>GRAND TOTAL</t>
+  </si>
+  <si>
+    <t>6.300,00</t>
+  </si>
+  <si>
+    <t>350,00</t>
+  </si>
+  <si>
+    <t>DILI, 18 August 2026</t>
+  </si>
+  <si>
+    <t>PREPARED BY</t>
+  </si>
+  <si>
+    <t>APPROVED BY</t>
+  </si>
+  <si>
+    <t>Human Resource</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Retail Senior Manager</t>
+  </si>
+  <si>
+    <t>Superadmin</t>
+  </si>
+  <si>
     <t>Lestari Putri Cantika</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Homestaff</t>
-  </si>
-  <si>
-    <t>550,00</t>
-  </si>
-  <si>
-    <t>1.650,00</t>
-  </si>
-  <si>
-    <t>165,00</t>
-  </si>
-  <si>
-    <t>HELENA</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
-    <t>FRIESCA AMELIA</t>
-  </si>
-  <si>
-    <t>III</t>
-  </si>
-  <si>
-    <t>Expat</t>
-  </si>
-  <si>
-    <t>0,00</t>
-  </si>
-  <si>
-    <t>55,00</t>
-  </si>
-  <si>
-    <t>Citra</t>
-  </si>
-  <si>
-    <t>dominika</t>
-  </si>
-  <si>
-    <t>IV</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>TEST BFKJ</t>
-  </si>
-  <si>
-    <t>5,00</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
-    <t>ADRIANTO LEBRE</t>
-  </si>
-  <si>
-    <t>100,00</t>
-  </si>
-  <si>
-    <t>300,00</t>
-  </si>
-  <si>
-    <t>0000002</t>
-  </si>
-  <si>
-    <t>Syifa Hadju</t>
-  </si>
-  <si>
-    <t>20,00</t>
-  </si>
-  <si>
-    <t>60,00</t>
-  </si>
-  <si>
-    <t>GRAND TOTAL</t>
-  </si>
-  <si>
-    <t>6.410,00</t>
-  </si>
-  <si>
-    <t>505,00</t>
-  </si>
-  <si>
-    <t>DILI, 14 August 2026</t>
-  </si>
-  <si>
-    <t>PREPARED BY</t>
-  </si>
-  <si>
-    <t>APPROVED BY</t>
-  </si>
-  <si>
-    <t>Human Resource</t>
-  </si>
-  <si>
-    <t>Marketing &amp; Retail Senior Manager</t>
-  </si>
-  <si>
-    <t>Superadmin</t>
   </si>
   <si>
     <t>NIK. 000002</t>
@@ -269,7 +254,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="514350" cy="333375"/>
@@ -588,13 +573,13 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="true" style="0"/>
-    <col min="2" max="2" width="25.851" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="38.848" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="8.141" bestFit="true" customWidth="true" style="0"/>
@@ -674,7 +659,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="3">
-        <v>999999</v>
+        <v>92003</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>15</v>
@@ -707,7 +692,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="3">
-        <v>84016</v>
+        <v>24016</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>21</v>
@@ -719,7 +704,7 @@
         <v>17</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
@@ -729,60 +714,60 @@
         <v>18</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="3">
-        <v>91009</v>
+        <v>74003</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="3">
-        <v>900145</v>
+        <v>95008</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>18</v>
@@ -792,262 +777,192 @@
         <v>18</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="3">
-        <v>83005</v>
+        <v>81010</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="3">
-        <v>83008</v>
+        <v>26013</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="K12" s="3" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="3">
-        <v>85014</v>
+        <v>91015</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>33</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="3">
-        <v>88015</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>37</v>
       </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>26</v>
+      <c r="K14" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="A15"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="G16"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J15" s="3" t="s">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18"/>
+      <c r="H18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" customHeight="1" ht="37.5">
+      <c r="A19"/>
+      <c r="E19"/>
+      <c r="H19"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20"/>
+      <c r="H20" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G18"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="5" t="s">
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5" t="s">
+      <c r="E21"/>
+      <c r="H21" t="s">
         <v>48</v>
-      </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20"/>
-      <c r="H20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" customHeight="1" ht="37.5">
-      <c r="A21"/>
-      <c r="E21"/>
-      <c r="H21"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22"/>
-      <c r="H22" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23"/>
-      <c r="H23" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1065,24 +980,24 @@
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="K5:K6"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="G18:K18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="F19:K19"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="G16:K16"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="F17:K17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="H19:K19"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="E20:G20"/>
     <mergeCell ref="H20:K20"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="E21:G21"/>
     <mergeCell ref="H21:K21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="H23:K23"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
